--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T15:39:37+00:00</t>
+    <t>2026-08-05T12:15:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T12:15:23+00:00</t>
+    <t>2026-08-11T08:03:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T08:03:55+00:00</t>
+    <t>2026-08-11T09:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T09:29:09+00:00</t>
+    <t>2026-08-13T09:45:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T09:45:33+00:00</t>
+    <t>2026-08-13T14:36:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-pregnancy-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1344" uniqueCount="202">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -475,6 +475,9 @@
   </si>
   <si>
     <t>Type d'observation</t>
+  </si>
+  <si>
+    <t>required</t>
   </si>
   <si>
     <t>jdv-issue-grossesse-cisis (1.2.250.1.213.1.1.5.731)</t>
@@ -3151,13 +3154,13 @@
         <v>73</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>73</v>
@@ -3192,10 +3195,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3221,10 +3224,10 @@
         <v>131</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3251,13 +3254,13 @@
         <v>73</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>73</v>
@@ -3275,7 +3278,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3292,10 +3295,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3321,10 +3324,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3375,7 +3378,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3392,10 +3395,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3418,13 +3421,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3475,7 +3478,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3492,10 +3495,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3521,10 +3524,10 @@
         <v>80</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3575,7 +3578,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3592,10 +3595,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3618,13 +3621,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3675,7 +3678,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -3692,10 +3695,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3718,13 +3721,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3775,7 +3778,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3792,10 +3795,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3821,10 +3824,10 @@
         <v>131</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3875,7 +3878,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3892,10 +3895,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3921,10 +3924,10 @@
         <v>80</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3975,7 +3978,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3992,10 +3995,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4018,13 +4021,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4075,7 +4078,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4092,10 +4095,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4118,13 +4121,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4175,7 +4178,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4192,10 +4195,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4221,10 +4224,10 @@
         <v>131</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4275,7 +4278,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
@@ -4292,10 +4295,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4321,10 +4324,10 @@
         <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4375,7 +4378,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
@@ -4392,10 +4395,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4421,10 +4424,10 @@
         <v>131</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4475,7 +4478,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>74</v>
@@ -4492,10 +4495,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4518,13 +4521,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4575,7 +4578,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>74</v>
@@ -4592,10 +4595,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4618,13 +4621,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4675,7 +4678,7 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -4692,10 +4695,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4721,10 +4724,10 @@
         <v>131</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4775,7 +4778,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -4792,10 +4795,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4818,13 +4821,13 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4875,7 +4878,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4892,10 +4895,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4921,10 +4924,10 @@
         <v>80</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4975,7 +4978,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4992,10 +4995,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5018,13 +5021,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5075,7 +5078,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -5092,10 +5095,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5118,13 +5121,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5175,7 +5178,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
